--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_3_burden_coverage_calibration_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_3_burden_coverage_calibration_source_data.xlsx
@@ -483,7 +483,7 @@
         <v>0.02040816326530612</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4897959183673469</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -508,7 +508,7 @@
         <v>0.5535714285714286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -530,10 +530,10 @@
         <v>45886</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6547619047619048</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -555,19 +555,19 @@
         <v>45893</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3089430894308943</v>
+        <v>0.311377245508982</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2845528455284553</v>
+        <v>0.2994011976047904</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7321428571428571</v>
+        <v>0.9940476190476191</v>
       </c>
       <c r="F5" t="n">
         <v>168</v>
       </c>
       <c r="G5" t="n">
-        <v>123</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6">
@@ -580,19 +580,19 @@
         <v>45900</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3087248322147651</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5302013422818792</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8869047619047619</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>168</v>
       </c>
       <c r="G6" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7">
@@ -605,19 +605,19 @@
         <v>45907</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8544303797468354</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1455696202531646</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9404761904761905</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>168</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
@@ -880,7 +880,7 @@
         <v>45984</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7440476190476191</v>
+        <v>0.75</v>
       </c>
       <c r="D18" t="n">
         <v>0.1726190476190476</v>
@@ -905,10 +905,10 @@
         <v>45991</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -980,10 +980,10 @@
         <v>46012</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -1005,10 +1005,10 @@
         <v>46019</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5178571428571429</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0119047619047619</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -1055,10 +1055,10 @@
         <v>46033</v>
       </c>
       <c r="C25" t="n">
-        <v>0.463768115942029</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3188405797101449</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="E25" t="n">
         <v>0.8214285714285714</v>
@@ -1080,10 +1080,10 @@
         <v>46040</v>
       </c>
       <c r="C26" t="n">
-        <v>0.125</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1105,10 +1105,10 @@
         <v>46047</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1130,10 +1130,10 @@
         <v>46054</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2976190476190476</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="D28" t="n">
-        <v>0.125</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -1155,10 +1155,10 @@
         <v>46061</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6488095238095238</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -1180,7 +1180,7 @@
         <v>46068</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="D30" t="n">
         <v>0.3690476190476191</v>
@@ -1205,10 +1205,10 @@
         <v>46075</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1845238095238095</v>
+        <v>0.1011904761904762</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.244047619047619</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1230,10 +1230,10 @@
         <v>46082</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4940476190476191</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1255,10 +1255,10 @@
         <v>46089</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6369047619047619</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3511904761904762</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1280,10 +1280,10 @@
         <v>46096</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -1305,19 +1305,19 @@
         <v>46103</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1224489795918367</v>
+        <v>0.1073825503355705</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1292517006802721</v>
+        <v>0.1275167785234899</v>
       </c>
       <c r="E35" t="n">
-        <v>0.875</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="F35" t="n">
         <v>168</v>
       </c>
       <c r="G35" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36">
@@ -1330,10 +1330,10 @@
         <v>46110</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.625</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1355,10 +1355,10 @@
         <v>46117</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4821428571428572</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1380,10 +1380,10 @@
         <v>46124</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7202380952380952</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="D38" t="n">
-        <v>0.244047619047619</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -1405,10 +1405,10 @@
         <v>46131</v>
       </c>
       <c r="C39" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="D39" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="E39" t="n">
         <v>0.8333333333333334</v>
@@ -1455,10 +1455,10 @@
         <v>45879</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -1480,10 +1480,10 @@
         <v>45886</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         <v>0.03571428571428571</v>
       </c>
       <c r="D43" t="n">
-        <v>0.8452380952380952</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -1533,7 +1533,7 @@
         <v>0.2023809523809524</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.7440476190476191</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -1583,7 +1583,7 @@
         <v>0.5655172413793104</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3862068965517241</v>
+        <v>0.3793103448275862</v>
       </c>
       <c r="E46" t="n">
         <v>0.8630952380952381</v>
@@ -1780,10 +1780,10 @@
         <v>45970</v>
       </c>
       <c r="C54" t="n">
-        <v>0.4702380952380952</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3035714285714285</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -1805,10 +1805,10 @@
         <v>45977</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5119047619047619</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1488095238095238</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -1830,7 +1830,7 @@
         <v>45984</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8154761904761905</v>
       </c>
       <c r="D56" t="n">
         <v>0.1011904761904762</v>
@@ -1858,7 +1858,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3630952380952381</v>
+        <v>0.3690476190476191</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -1905,10 +1905,10 @@
         <v>46005</v>
       </c>
       <c r="C59" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1845238095238095</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -1955,10 +1955,10 @@
         <v>46019</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -1980,10 +1980,10 @@
         <v>46026</v>
       </c>
       <c r="C62" t="n">
-        <v>0.4821428571428572</v>
+        <v>0.4345238095238095</v>
       </c>
       <c r="D62" t="n">
-        <v>0.3690476190476191</v>
+        <v>0.3869047619047619</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -2005,10 +2005,10 @@
         <v>46033</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6811594202898551</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1594202898550725</v>
+        <v>0.1884057971014493</v>
       </c>
       <c r="E63" t="n">
         <v>0.8214285714285714</v>
@@ -2030,10 +2030,10 @@
         <v>46040</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -2055,10 +2055,10 @@
         <v>46047</v>
       </c>
       <c r="C65" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="D65" t="n">
-        <v>0.2559523809523809</v>
+        <v>0.25</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -2083,7 +2083,7 @@
         <v>0.07738095238095238</v>
       </c>
       <c r="D66" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.05952380952380952</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -2105,10 +2105,10 @@
         <v>46061</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.1488095238095238</v>
       </c>
       <c r="D67" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -2130,10 +2130,10 @@
         <v>46068</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.1011904761904762</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4404761904761905</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -2155,10 +2155,10 @@
         <v>46075</v>
       </c>
       <c r="C69" t="n">
-        <v>0.7976190476190477</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D69" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -2180,10 +2180,10 @@
         <v>46082</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -2205,10 +2205,10 @@
         <v>46089</v>
       </c>
       <c r="C71" t="n">
-        <v>0.119047619047619</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4404761904761905</v>
+        <v>0.4345238095238095</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -2255,19 +2255,19 @@
         <v>46103</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1148648648648649</v>
+        <v>0.1140939597315436</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4189189189189189</v>
+        <v>0.4161073825503356</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="F73" t="n">
         <v>168</v>
       </c>
       <c r="G73" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74">
@@ -2280,10 +2280,10 @@
         <v>46110</v>
       </c>
       <c r="C74" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="D74" t="n">
         <v>0.1785714285714286</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.1547619047619048</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2305,10 +2305,10 @@
         <v>46117</v>
       </c>
       <c r="C75" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3869047619047619</v>
+        <v>0.3630952380952381</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -2330,10 +2330,10 @@
         <v>46124</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.2678571428571428</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -2355,10 +2355,10 @@
         <v>46131</v>
       </c>
       <c r="C77" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="D77" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E77" t="n">
         <v>0.8333333333333334</v>
@@ -2405,10 +2405,10 @@
         <v>45879</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3511904761904762</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
@@ -2430,7 +2430,7 @@
         <v>45886</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.125</v>
       </c>
       <c r="D80" t="n">
         <v>0.2321428571428572</v>
@@ -2458,7 +2458,7 @@
         <v>0.2202380952380952</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6547619047619048</v>
+        <v>0.6607142857142857</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2480,10 +2480,10 @@
         <v>45900</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="D82" t="n">
-        <v>0.5773809523809523</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -2505,10 +2505,10 @@
         <v>45907</v>
       </c>
       <c r="C83" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.4226190476190476</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -2530,7 +2530,7 @@
         <v>45914</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3931034482758621</v>
+        <v>0.3862068965517241</v>
       </c>
       <c r="D84" t="n">
         <v>0.1517241379310345</v>
@@ -2680,10 +2680,10 @@
         <v>45956</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.2797619047619048</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -2705,10 +2705,10 @@
         <v>45963</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="D91" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
@@ -2730,7 +2730,7 @@
         <v>45970</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.3511904761904762</v>
       </c>
       <c r="D92" t="n">
         <v>0.2083333333333333</v>
@@ -2755,10 +2755,10 @@
         <v>45977</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -2780,7 +2780,7 @@
         <v>45984</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.3988095238095238</v>
       </c>
       <c r="D94" t="n">
         <v>0.4107142857142857</v>
@@ -2805,10 +2805,10 @@
         <v>45991</v>
       </c>
       <c r="C95" t="n">
-        <v>0.3511904761904762</v>
+        <v>0.375</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -2833,7 +2833,7 @@
         <v>0.07738095238095238</v>
       </c>
       <c r="D96" t="n">
-        <v>0.5</v>
+        <v>0.5119047619047619</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
@@ -2858,7 +2858,7 @@
         <v>0.3154761904761905</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -2880,10 +2880,10 @@
         <v>46012</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.3511904761904762</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1845238095238095</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
@@ -2905,10 +2905,10 @@
         <v>46019</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7202380952380952</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="D99" t="n">
-        <v>0.25</v>
+        <v>0.3273809523809524</v>
       </c>
       <c r="E99" t="n">
         <v>1</v>
@@ -2930,10 +2930,10 @@
         <v>46026</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3630952380952381</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
@@ -2955,10 +2955,10 @@
         <v>46033</v>
       </c>
       <c r="C101" t="n">
-        <v>0.355072463768116</v>
+        <v>0.2536231884057971</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2826086956521739</v>
+        <v>0.3405797101449275</v>
       </c>
       <c r="E101" t="n">
         <v>0.8214285714285714</v>
@@ -2980,10 +2980,10 @@
         <v>46040</v>
       </c>
       <c r="C102" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.2321428571428572</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.244047619047619</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -3005,10 +3005,10 @@
         <v>46047</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.6309523809523809</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.2678571428571428</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
@@ -3030,10 +3030,10 @@
         <v>46054</v>
       </c>
       <c r="C104" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3273809523809524</v>
+        <v>0.375</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
@@ -3055,10 +3055,10 @@
         <v>46061</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.5297619047619048</v>
       </c>
       <c r="D105" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -3080,10 +3080,10 @@
         <v>46068</v>
       </c>
       <c r="C106" t="n">
-        <v>0.75</v>
+        <v>0.6607142857142857</v>
       </c>
       <c r="D106" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -3105,10 +3105,10 @@
         <v>46075</v>
       </c>
       <c r="C107" t="n">
-        <v>0.7261904761904762</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="D107" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E107" t="n">
         <v>1</v>
@@ -3130,10 +3130,10 @@
         <v>46082</v>
       </c>
       <c r="C108" t="n">
-        <v>0.6607142857142857</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="D108" t="n">
-        <v>0.1488095238095238</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -3155,10 +3155,10 @@
         <v>46089</v>
       </c>
       <c r="C109" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.6130952380952381</v>
       </c>
       <c r="D109" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -3180,10 +3180,10 @@
         <v>46096</v>
       </c>
       <c r="C110" t="n">
-        <v>0.7202380952380952</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="D110" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
@@ -3205,10 +3205,10 @@
         <v>46103</v>
       </c>
       <c r="C111" t="n">
-        <v>0.7114093959731543</v>
+        <v>0.5973154362416108</v>
       </c>
       <c r="D111" t="n">
-        <v>0.1476510067114094</v>
+        <v>0.261744966442953</v>
       </c>
       <c r="E111" t="n">
         <v>0.8869047619047619</v>
@@ -3230,10 +3230,10 @@
         <v>46110</v>
       </c>
       <c r="C112" t="n">
-        <v>0.7559523809523809</v>
+        <v>0.6369047619047619</v>
       </c>
       <c r="D112" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -3255,10 +3255,10 @@
         <v>46117</v>
       </c>
       <c r="C113" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D113" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -3280,10 +3280,10 @@
         <v>46124</v>
       </c>
       <c r="C114" t="n">
-        <v>0.6904761904761905</v>
+        <v>0.6011904761904762</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1488095238095238</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -3330,10 +3330,10 @@
         <v>45872</v>
       </c>
       <c r="C116" t="n">
-        <v>0.4489795918367347</v>
+        <v>0.4693877551020408</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2448979591836735</v>
+        <v>0.2244897959183673</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3355,10 +3355,10 @@
         <v>45879</v>
       </c>
       <c r="C117" t="n">
-        <v>0.4226190476190476</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="D117" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.1488095238095238</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
@@ -3380,10 +3380,10 @@
         <v>45886</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5773809523809523</v>
+        <v>0.5595238095238095</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="E118" t="n">
         <v>1</v>
@@ -3458,7 +3458,7 @@
         <v>0.5357142857142857</v>
       </c>
       <c r="D121" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -3630,10 +3630,10 @@
         <v>45956</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D128" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.1011904761904762</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
@@ -3655,10 +3655,10 @@
         <v>45963</v>
       </c>
       <c r="C129" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D129" t="n">
-        <v>0.119047619047619</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="E129" t="n">
         <v>1</v>
@@ -3680,10 +3680,10 @@
         <v>45970</v>
       </c>
       <c r="C130" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.625</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -3730,10 +3730,10 @@
         <v>45984</v>
       </c>
       <c r="C132" t="n">
-        <v>0.5</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="D132" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2559523809523809</v>
+        <v>0.2678571428571428</v>
       </c>
       <c r="E133" t="n">
         <v>1</v>
@@ -3783,7 +3783,7 @@
         <v>0.1904761904761905</v>
       </c>
       <c r="D134" t="n">
-        <v>0.5178571428571429</v>
+        <v>0.5297619047619048</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -3855,10 +3855,10 @@
         <v>46019</v>
       </c>
       <c r="C137" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="E137" t="n">
         <v>1</v>
@@ -3905,10 +3905,10 @@
         <v>46033</v>
       </c>
       <c r="C139" t="n">
-        <v>0.6014492753623188</v>
+        <v>0.5579710144927537</v>
       </c>
       <c r="D139" t="n">
-        <v>0.09420289855072464</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="E139" t="n">
         <v>0.8214285714285714</v>
@@ -3930,10 +3930,10 @@
         <v>46040</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="E140" t="n">
         <v>1</v>
@@ -3955,10 +3955,10 @@
         <v>46047</v>
       </c>
       <c r="C141" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.125</v>
       </c>
       <c r="E141" t="n">
         <v>1</v>
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1845238095238095</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="E142" t="n">
         <v>1</v>
@@ -4005,10 +4005,10 @@
         <v>46061</v>
       </c>
       <c r="C143" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3035714285714285</v>
       </c>
       <c r="E143" t="n">
         <v>1</v>
@@ -4030,10 +4030,10 @@
         <v>46068</v>
       </c>
       <c r="C144" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="D144" t="n">
-        <v>0.6904761904761905</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -4055,10 +4055,10 @@
         <v>46075</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1845238095238095</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="D145" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
@@ -4080,10 +4080,10 @@
         <v>46082</v>
       </c>
       <c r="C146" t="n">
-        <v>0.04166666666666666</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
@@ -4105,10 +4105,10 @@
         <v>46089</v>
       </c>
       <c r="C147" t="n">
-        <v>0.3392857142857143</v>
+        <v>0.2976190476190476</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4130,10 +4130,10 @@
         <v>46096</v>
       </c>
       <c r="C148" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E148" t="n">
         <v>1</v>
@@ -4155,10 +4155,10 @@
         <v>46103</v>
       </c>
       <c r="C149" t="n">
-        <v>0.3691275167785235</v>
+        <v>0.3154362416107382</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3557046979865772</v>
+        <v>0.4161073825503356</v>
       </c>
       <c r="E149" t="n">
         <v>0.8869047619047619</v>
@@ -4180,10 +4180,10 @@
         <v>46110</v>
       </c>
       <c r="C150" t="n">
-        <v>0.02380952380952381</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="E150" t="n">
         <v>1</v>
@@ -4205,7 +4205,7 @@
         <v>46117</v>
       </c>
       <c r="C151" t="n">
-        <v>0.01785714285714286</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
         <v>0.7738095238095238</v>
@@ -4230,10 +4230,10 @@
         <v>46124</v>
       </c>
       <c r="C152" t="n">
-        <v>0.7976190476190477</v>
+        <v>0.6309523809523809</v>
       </c>
       <c r="D152" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.3630952380952381</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -4255,10 +4255,10 @@
         <v>46131</v>
       </c>
       <c r="C153" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D153" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E153" t="n">
         <v>0.8333333333333334</v>
@@ -4280,19 +4280,19 @@
         <v>45872</v>
       </c>
       <c r="C154" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="D154" t="n">
-        <v>0.625</v>
+        <v>0.6530612244897959</v>
       </c>
       <c r="E154" t="n">
-        <v>0.9795918367346939</v>
+        <v>1</v>
       </c>
       <c r="F154" t="n">
         <v>49</v>
       </c>
       <c r="G154" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="155">
@@ -4305,19 +4305,19 @@
         <v>45879</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.4226190476190476</v>
       </c>
       <c r="D155" t="n">
-        <v>0.1895424836601307</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="E155" t="n">
-        <v>0.9107142857142857</v>
+        <v>1</v>
       </c>
       <c r="F155" t="n">
         <v>168</v>
       </c>
       <c r="G155" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="156">
@@ -4330,19 +4330,19 @@
         <v>45886</v>
       </c>
       <c r="C156" t="n">
-        <v>0.15625</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="D156" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="E156" t="n">
-        <v>0.9523809523809523</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
         <v>168</v>
       </c>
       <c r="G156" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="157">
@@ -4355,19 +4355,19 @@
         <v>45893</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0783132530120482</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="D157" t="n">
-        <v>0.5843373493975904</v>
+        <v>0.6369047619047619</v>
       </c>
       <c r="E157" t="n">
-        <v>0.9880952380952381</v>
+        <v>1</v>
       </c>
       <c r="F157" t="n">
         <v>168</v>
       </c>
       <c r="G157" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="158">
@@ -4383,16 +4383,16 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0.7861635220125787</v>
+        <v>0.7797619047619048</v>
       </c>
       <c r="E158" t="n">
-        <v>0.9464285714285714</v>
+        <v>1</v>
       </c>
       <c r="F158" t="n">
         <v>168</v>
       </c>
       <c r="G158" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="159">
@@ -4405,19 +4405,19 @@
         <v>45907</v>
       </c>
       <c r="C159" t="n">
-        <v>0.05</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2928571428571429</v>
+        <v>0.2797619047619048</v>
       </c>
       <c r="E159" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
         <v>168</v>
       </c>
       <c r="G159" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
     </row>
     <row r="160">
@@ -4430,19 +4430,19 @@
         <v>45914</v>
       </c>
       <c r="C160" t="n">
-        <v>0.390625</v>
+        <v>0.3724137931034483</v>
       </c>
       <c r="D160" t="n">
-        <v>0.1171875</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="E160" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.8630952380952381</v>
       </c>
       <c r="F160" t="n">
         <v>168</v>
       </c>
       <c r="G160" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
     <row r="161">
@@ -4455,19 +4455,19 @@
         <v>45921</v>
       </c>
       <c r="C161" t="n">
-        <v>0.8258064516129032</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1483870967741935</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E161" t="n">
-        <v>0.9226190476190477</v>
+        <v>1</v>
       </c>
       <c r="F161" t="n">
         <v>168</v>
       </c>
       <c r="G161" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="162">
@@ -4480,19 +4480,19 @@
         <v>45928</v>
       </c>
       <c r="C162" t="n">
-        <v>0.2215568862275449</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="D162" t="n">
-        <v>0.2694610778443114</v>
+        <v>0.25</v>
       </c>
       <c r="E162" t="n">
-        <v>0.9940476190476191</v>
+        <v>1</v>
       </c>
       <c r="F162" t="n">
         <v>168</v>
       </c>
       <c r="G162" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="163">
@@ -4505,10 +4505,10 @@
         <v>45935</v>
       </c>
       <c r="C163" t="n">
-        <v>0.4880952380952381</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4345238095238095</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="E163" t="n">
         <v>1</v>
@@ -4530,10 +4530,10 @@
         <v>45942</v>
       </c>
       <c r="C164" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="E164" t="n">
         <v>1</v>
@@ -4555,19 +4555,19 @@
         <v>45949</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1025641025641026</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4226190476190476</v>
       </c>
       <c r="E165" t="n">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
       <c r="F165" t="n">
         <v>168</v>
       </c>
       <c r="G165" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166">
@@ -4580,19 +4580,19 @@
         <v>45956</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4451219512195122</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D166" t="n">
-        <v>0.1585365853658537</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="E166" t="n">
-        <v>0.9761904761904762</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
         <v>168</v>
       </c>
       <c r="G166" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="167">
@@ -4605,10 +4605,10 @@
         <v>45963</v>
       </c>
       <c r="C167" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.0119047619047619</v>
       </c>
       <c r="D167" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
@@ -4630,19 +4630,19 @@
         <v>45970</v>
       </c>
       <c r="C168" t="n">
-        <v>0.6227544910179641</v>
+        <v>0.6309523809523809</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1377245508982036</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="E168" t="n">
-        <v>0.9940476190476191</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
         <v>168</v>
       </c>
       <c r="G168" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="169">
@@ -4655,19 +4655,19 @@
         <v>45977</v>
       </c>
       <c r="C169" t="n">
-        <v>0.3395061728395062</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="D169" t="n">
-        <v>0.382716049382716</v>
+        <v>0.375</v>
       </c>
       <c r="E169" t="n">
-        <v>0.9642857142857143</v>
+        <v>1</v>
       </c>
       <c r="F169" t="n">
         <v>168</v>
       </c>
       <c r="G169" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="170">
@@ -4680,19 +4680,19 @@
         <v>45984</v>
       </c>
       <c r="C170" t="n">
-        <v>0.2420382165605096</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="D170" t="n">
-        <v>0.2547770700636943</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="E170" t="n">
-        <v>0.9345238095238095</v>
+        <v>1</v>
       </c>
       <c r="F170" t="n">
         <v>168</v>
       </c>
       <c r="G170" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="171">
@@ -4708,16 +4708,16 @@
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0.01418439716312057</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>0.8392857142857143</v>
+        <v>1</v>
       </c>
       <c r="F171" t="n">
         <v>168</v>
       </c>
       <c r="G171" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
     </row>
     <row r="172">
@@ -4730,19 +4730,19 @@
         <v>45998</v>
       </c>
       <c r="C172" t="n">
-        <v>0.02158273381294964</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="D172" t="n">
-        <v>0.1726618705035971</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="E172" t="n">
-        <v>0.8273809523809523</v>
+        <v>1</v>
       </c>
       <c r="F172" t="n">
         <v>168</v>
       </c>
       <c r="G172" t="n">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="173">
@@ -4755,19 +4755,19 @@
         <v>46005</v>
       </c>
       <c r="C173" t="n">
-        <v>0.2180451127819549</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D173" t="n">
-        <v>0.2556390977443609</v>
+        <v>0.2976190476190476</v>
       </c>
       <c r="E173" t="n">
-        <v>0.7916666666666666</v>
+        <v>1</v>
       </c>
       <c r="F173" t="n">
         <v>168</v>
       </c>
       <c r="G173" t="n">
-        <v>133</v>
+        <v>168</v>
       </c>
     </row>
     <row r="174">
@@ -4780,19 +4780,19 @@
         <v>46012</v>
       </c>
       <c r="C174" t="n">
-        <v>0.2394366197183098</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="D174" t="n">
-        <v>0.007042253521126761</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="E174" t="n">
-        <v>0.8452380952380952</v>
+        <v>1</v>
       </c>
       <c r="F174" t="n">
         <v>168</v>
       </c>
       <c r="G174" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
     </row>
     <row r="175">
@@ -4805,19 +4805,19 @@
         <v>46019</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3907284768211921</v>
+        <v>0.3511904761904762</v>
       </c>
       <c r="D175" t="n">
-        <v>0.1721854304635762</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="E175" t="n">
-        <v>0.8988095238095238</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
         <v>168</v>
       </c>
       <c r="G175" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="176">
@@ -4830,19 +4830,19 @@
         <v>46026</v>
       </c>
       <c r="C176" t="n">
-        <v>0.310126582278481</v>
+        <v>0.244047619047619</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4367088607594937</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="E176" t="n">
-        <v>0.9404761904761905</v>
+        <v>1</v>
       </c>
       <c r="F176" t="n">
         <v>168</v>
       </c>
       <c r="G176" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="177">
@@ -4855,19 +4855,19 @@
         <v>46033</v>
       </c>
       <c r="C177" t="n">
-        <v>0.04587155963302753</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="D177" t="n">
-        <v>0.3211009174311927</v>
+        <v>0.2753623188405797</v>
       </c>
       <c r="E177" t="n">
-        <v>0.6488095238095238</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="F177" t="n">
         <v>168</v>
       </c>
       <c r="G177" t="n">
-        <v>109</v>
+        <v>138</v>
       </c>
     </row>
     <row r="178">
@@ -4880,19 +4880,19 @@
         <v>46040</v>
       </c>
       <c r="C178" t="n">
-        <v>0.006289308176100629</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="D178" t="n">
-        <v>0.1572327044025157</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="E178" t="n">
-        <v>0.9464285714285714</v>
+        <v>1</v>
       </c>
       <c r="F178" t="n">
         <v>168</v>
       </c>
       <c r="G178" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="179">
@@ -4905,19 +4905,19 @@
         <v>46047</v>
       </c>
       <c r="C179" t="n">
-        <v>0.04819277108433735</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="D179" t="n">
-        <v>0.1506024096385542</v>
+        <v>0.125</v>
       </c>
       <c r="E179" t="n">
-        <v>0.9880952380952381</v>
+        <v>1</v>
       </c>
       <c r="F179" t="n">
         <v>168</v>
       </c>
       <c r="G179" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="180">
@@ -4930,19 +4930,19 @@
         <v>46054</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1796407185628743</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="D180" t="n">
-        <v>0.3233532934131736</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E180" t="n">
-        <v>0.9940476190476191</v>
+        <v>1</v>
       </c>
       <c r="F180" t="n">
         <v>168</v>
       </c>
       <c r="G180" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="181">
@@ -4955,19 +4955,19 @@
         <v>46061</v>
       </c>
       <c r="C181" t="n">
-        <v>0.3493975903614458</v>
+        <v>0.2678571428571428</v>
       </c>
       <c r="D181" t="n">
-        <v>0.3614457831325301</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="E181" t="n">
-        <v>0.9880952380952381</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
         <v>168</v>
       </c>
       <c r="G181" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="182">
@@ -4980,19 +4980,19 @@
         <v>46068</v>
       </c>
       <c r="C182" t="n">
-        <v>0.2181818181818182</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="D182" t="n">
-        <v>0.3878787878787879</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="E182" t="n">
-        <v>0.9821428571428571</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
         <v>168</v>
       </c>
       <c r="G182" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="183">
@@ -5005,19 +5005,19 @@
         <v>46075</v>
       </c>
       <c r="C183" t="n">
-        <v>0.4748201438848921</v>
+        <v>0.3511904761904762</v>
       </c>
       <c r="D183" t="n">
-        <v>0.09352517985611511</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="E183" t="n">
-        <v>0.8273809523809523</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
         <v>168</v>
       </c>
       <c r="G183" t="n">
-        <v>139</v>
+        <v>168</v>
       </c>
     </row>
     <row r="184">
@@ -5030,19 +5030,19 @@
         <v>46082</v>
       </c>
       <c r="C184" t="n">
-        <v>0.02424242424242424</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="D184" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.05357142857142857</v>
       </c>
       <c r="E184" t="n">
-        <v>0.9821428571428571</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
         <v>168</v>
       </c>
       <c r="G184" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="185">
@@ -5055,19 +5055,19 @@
         <v>46089</v>
       </c>
       <c r="C185" t="n">
-        <v>0.2378048780487805</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="D185" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="E185" t="n">
-        <v>0.9761904761904762</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
         <v>168</v>
       </c>
       <c r="G185" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="186">
@@ -5080,19 +5080,19 @@
         <v>46096</v>
       </c>
       <c r="C186" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D186" t="n">
-        <v>0.2407407407407407</v>
+        <v>0.2321428571428572</v>
       </c>
       <c r="E186" t="n">
-        <v>0.9642857142857143</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
         <v>168</v>
       </c>
       <c r="G186" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="187">
@@ -5105,19 +5105,19 @@
         <v>46103</v>
       </c>
       <c r="C187" t="n">
-        <v>0.5949367088607594</v>
+        <v>0.5654761904761905</v>
       </c>
       <c r="D187" t="n">
-        <v>0.1392405063291139</v>
+        <v>0.125</v>
       </c>
       <c r="E187" t="n">
-        <v>0.9404761904761905</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
         <v>168</v>
       </c>
       <c r="G187" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="188">
@@ -5130,19 +5130,19 @@
         <v>46110</v>
       </c>
       <c r="C188" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D188" t="n">
-        <v>0.0457516339869281</v>
+        <v>0.05952380952380952</v>
       </c>
       <c r="E188" t="n">
-        <v>0.9107142857142857</v>
+        <v>1</v>
       </c>
       <c r="F188" t="n">
         <v>168</v>
       </c>
       <c r="G188" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="189">
@@ -5155,19 +5155,19 @@
         <v>46117</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4509803921568628</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="D189" t="n">
-        <v>0.2026143790849673</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E189" t="n">
-        <v>0.9107142857142857</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
         <v>168</v>
       </c>
       <c r="G189" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="190">
@@ -5180,19 +5180,19 @@
         <v>46124</v>
       </c>
       <c r="C190" t="n">
-        <v>0.2838709677419355</v>
+        <v>0.25</v>
       </c>
       <c r="D190" t="n">
-        <v>0.232258064516129</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="E190" t="n">
-        <v>0.9226190476190477</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
         <v>168</v>
       </c>
       <c r="G190" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="191">
@@ -5211,13 +5211,13 @@
         <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F191" t="n">
         <v>24</v>
       </c>
       <c r="G191" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192">
@@ -5255,19 +5255,19 @@
         <v>45879</v>
       </c>
       <c r="C193" t="n">
-        <v>0.2345679012345679</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="D193" t="n">
-        <v>0.1728395061728395</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="E193" t="n">
-        <v>0.9642857142857143</v>
+        <v>1</v>
       </c>
       <c r="F193" t="n">
         <v>168</v>
       </c>
       <c r="G193" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="194">
@@ -5280,10 +5280,10 @@
         <v>45886</v>
       </c>
       <c r="C194" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.3690476190476191</v>
       </c>
       <c r="D194" t="n">
-        <v>0.4880952380952381</v>
+        <v>0.5</v>
       </c>
       <c r="E194" t="n">
         <v>1</v>
@@ -5305,19 +5305,19 @@
         <v>45893</v>
       </c>
       <c r="C195" t="n">
-        <v>0.1153846153846154</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="D195" t="n">
-        <v>0.108974358974359</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="E195" t="n">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
         <v>168</v>
       </c>
       <c r="G195" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="196">
@@ -5330,10 +5330,10 @@
         <v>45900</v>
       </c>
       <c r="C196" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="D196" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.3690476190476191</v>
       </c>
       <c r="E196" t="n">
         <v>1</v>
@@ -5355,19 +5355,19 @@
         <v>45907</v>
       </c>
       <c r="C197" t="n">
-        <v>0.3548387096774194</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="D197" t="n">
-        <v>0.2967741935483871</v>
+        <v>0.375</v>
       </c>
       <c r="E197" t="n">
-        <v>0.9226190476190477</v>
+        <v>1</v>
       </c>
       <c r="F197" t="n">
         <v>168</v>
       </c>
       <c r="G197" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="198">
@@ -5380,19 +5380,19 @@
         <v>45914</v>
       </c>
       <c r="C198" t="n">
-        <v>0.107843137254902</v>
+        <v>0.08275862068965517</v>
       </c>
       <c r="D198" t="n">
-        <v>0.1372549019607843</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="E198" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.8630952380952381</v>
       </c>
       <c r="F198" t="n">
         <v>168</v>
       </c>
       <c r="G198" t="n">
-        <v>102</v>
+        <v>145</v>
       </c>
     </row>
     <row r="199">
@@ -5405,19 +5405,19 @@
         <v>45921</v>
       </c>
       <c r="C199" t="n">
-        <v>0.7341772151898734</v>
+        <v>0.6726190476190477</v>
       </c>
       <c r="D199" t="n">
-        <v>0.08860759493670886</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="E199" t="n">
-        <v>0.4702380952380952</v>
+        <v>1</v>
       </c>
       <c r="F199" t="n">
         <v>168</v>
       </c>
       <c r="G199" t="n">
-        <v>79</v>
+        <v>168</v>
       </c>
     </row>
     <row r="200">
@@ -5430,19 +5430,19 @@
         <v>45928</v>
       </c>
       <c r="C200" t="n">
-        <v>0.6825396825396826</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="D200" t="n">
-        <v>0.1349206349206349</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E200" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F200" t="n">
         <v>168</v>
       </c>
       <c r="G200" t="n">
-        <v>126</v>
+        <v>168</v>
       </c>
     </row>
     <row r="201">
@@ -5455,19 +5455,19 @@
         <v>45935</v>
       </c>
       <c r="C201" t="n">
-        <v>0.1854304635761589</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="D201" t="n">
-        <v>0.1655629139072848</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="E201" t="n">
-        <v>0.8988095238095238</v>
+        <v>1</v>
       </c>
       <c r="F201" t="n">
         <v>168</v>
       </c>
       <c r="G201" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="202">
@@ -5480,19 +5480,19 @@
         <v>45942</v>
       </c>
       <c r="C202" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D202" t="n">
-        <v>0.2348484848484849</v>
+        <v>0.2797619047619048</v>
       </c>
       <c r="E202" t="n">
-        <v>0.7857142857142857</v>
+        <v>1</v>
       </c>
       <c r="F202" t="n">
         <v>168</v>
       </c>
       <c r="G202" t="n">
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="203">
@@ -5505,19 +5505,19 @@
         <v>45949</v>
       </c>
       <c r="C203" t="n">
-        <v>0.3493150684931507</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="D203" t="n">
-        <v>0.1712328767123288</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="E203" t="n">
-        <v>0.8690476190476191</v>
+        <v>1</v>
       </c>
       <c r="F203" t="n">
         <v>168</v>
       </c>
       <c r="G203" t="n">
-        <v>146</v>
+        <v>168</v>
       </c>
     </row>
     <row r="204">
@@ -5530,19 +5530,19 @@
         <v>45956</v>
       </c>
       <c r="C204" t="n">
-        <v>0.256</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="D204" t="n">
-        <v>0.176</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E204" t="n">
-        <v>0.7440476190476191</v>
+        <v>1</v>
       </c>
       <c r="F204" t="n">
         <v>168</v>
       </c>
       <c r="G204" t="n">
-        <v>125</v>
+        <v>168</v>
       </c>
     </row>
     <row r="205">
@@ -5555,19 +5555,19 @@
         <v>45963</v>
       </c>
       <c r="C205" t="n">
-        <v>0.7246376811594203</v>
+        <v>0.6845238095238095</v>
       </c>
       <c r="D205" t="n">
-        <v>0.2681159420289855</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="E205" t="n">
-        <v>0.8214285714285714</v>
+        <v>1</v>
       </c>
       <c r="F205" t="n">
         <v>168</v>
       </c>
       <c r="G205" t="n">
-        <v>138</v>
+        <v>168</v>
       </c>
     </row>
     <row r="206">
@@ -5580,19 +5580,19 @@
         <v>45970</v>
       </c>
       <c r="C206" t="n">
-        <v>0.08088235294117647</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="D206" t="n">
-        <v>0.04411764705882353</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="E206" t="n">
-        <v>0.8095238095238095</v>
+        <v>1</v>
       </c>
       <c r="F206" t="n">
         <v>168</v>
       </c>
       <c r="G206" t="n">
-        <v>136</v>
+        <v>168</v>
       </c>
     </row>
     <row r="207">
@@ -5605,19 +5605,19 @@
         <v>45977</v>
       </c>
       <c r="C207" t="n">
-        <v>0.2</v>
+        <v>0.1845238095238095</v>
       </c>
       <c r="D207" t="n">
-        <v>0.1793103448275862</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="E207" t="n">
-        <v>0.8630952380952381</v>
+        <v>1</v>
       </c>
       <c r="F207" t="n">
         <v>168</v>
       </c>
       <c r="G207" t="n">
-        <v>145</v>
+        <v>168</v>
       </c>
     </row>
     <row r="208">
@@ -5630,19 +5630,19 @@
         <v>45984</v>
       </c>
       <c r="C208" t="n">
-        <v>0.2866666666666667</v>
+        <v>0.2797619047619048</v>
       </c>
       <c r="D208" t="n">
-        <v>0.26</v>
+        <v>0.244047619047619</v>
       </c>
       <c r="E208" t="n">
-        <v>0.8928571428571429</v>
+        <v>1</v>
       </c>
       <c r="F208" t="n">
         <v>168</v>
       </c>
       <c r="G208" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="209">
@@ -5655,19 +5655,19 @@
         <v>45991</v>
       </c>
       <c r="C209" t="n">
-        <v>0.2645161290322581</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="D209" t="n">
-        <v>0.2516129032258064</v>
+        <v>0.25</v>
       </c>
       <c r="E209" t="n">
-        <v>0.9226190476190477</v>
+        <v>1</v>
       </c>
       <c r="F209" t="n">
         <v>168</v>
       </c>
       <c r="G209" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="210">
@@ -5680,19 +5680,19 @@
         <v>45998</v>
       </c>
       <c r="C210" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="D210" t="n">
-        <v>0.2657342657342657</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="E210" t="n">
-        <v>0.8511904761904762</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
         <v>168</v>
       </c>
       <c r="G210" t="n">
-        <v>143</v>
+        <v>168</v>
       </c>
     </row>
     <row r="211">
@@ -5705,19 +5705,19 @@
         <v>46005</v>
       </c>
       <c r="C211" t="n">
-        <v>0.2483660130718954</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="D211" t="n">
-        <v>0.1830065359477124</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E211" t="n">
-        <v>0.9107142857142857</v>
+        <v>1</v>
       </c>
       <c r="F211" t="n">
         <v>168</v>
       </c>
       <c r="G211" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="212">
@@ -5730,19 +5730,19 @@
         <v>46012</v>
       </c>
       <c r="C212" t="n">
-        <v>0.4539877300613497</v>
+        <v>0.4345238095238095</v>
       </c>
       <c r="D212" t="n">
-        <v>0.2576687116564417</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="E212" t="n">
-        <v>0.9702380952380952</v>
+        <v>1</v>
       </c>
       <c r="F212" t="n">
         <v>168</v>
       </c>
       <c r="G212" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="213">
@@ -5755,19 +5755,19 @@
         <v>46019</v>
       </c>
       <c r="C213" t="n">
-        <v>0.9869281045751634</v>
+        <v>0.9880952380952381</v>
       </c>
       <c r="D213" t="n">
-        <v>0.0130718954248366</v>
+        <v>0.0119047619047619</v>
       </c>
       <c r="E213" t="n">
-        <v>0.9107142857142857</v>
+        <v>1</v>
       </c>
       <c r="F213" t="n">
         <v>168</v>
       </c>
       <c r="G213" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="214">
@@ -5786,13 +5786,13 @@
         <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>0.8154761904761905</v>
+        <v>1</v>
       </c>
       <c r="F214" t="n">
         <v>168</v>
       </c>
       <c r="G214" t="n">
-        <v>137</v>
+        <v>168</v>
       </c>
     </row>
     <row r="215">
@@ -5805,19 +5805,19 @@
         <v>46033</v>
       </c>
       <c r="C215" t="n">
-        <v>0.8468468468468469</v>
+        <v>0.8623188405797102</v>
       </c>
       <c r="D215" t="n">
-        <v>0.05405405405405406</v>
+        <v>0.05797101449275362</v>
       </c>
       <c r="E215" t="n">
-        <v>0.6607142857142857</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="F215" t="n">
         <v>168</v>
       </c>
       <c r="G215" t="n">
-        <v>111</v>
+        <v>138</v>
       </c>
     </row>
     <row r="216">
@@ -5830,19 +5830,19 @@
         <v>46040</v>
       </c>
       <c r="C216" t="n">
-        <v>0.562962962962963</v>
+        <v>0.5119047619047619</v>
       </c>
       <c r="D216" t="n">
-        <v>0.3037037037037037</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E216" t="n">
-        <v>0.8035714285714286</v>
+        <v>1</v>
       </c>
       <c r="F216" t="n">
         <v>168</v>
       </c>
       <c r="G216" t="n">
-        <v>135</v>
+        <v>168</v>
       </c>
     </row>
     <row r="217">
@@ -5855,19 +5855,19 @@
         <v>46047</v>
       </c>
       <c r="C217" t="n">
-        <v>0.3592233009708738</v>
+        <v>0.1488095238095238</v>
       </c>
       <c r="D217" t="n">
-        <v>0.2330097087378641</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E217" t="n">
-        <v>0.6130952380952381</v>
+        <v>1</v>
       </c>
       <c r="F217" t="n">
         <v>168</v>
       </c>
       <c r="G217" t="n">
-        <v>103</v>
+        <v>168</v>
       </c>
     </row>
     <row r="218">
@@ -5880,19 +5880,19 @@
         <v>46054</v>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="E218" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
         <v>168</v>
       </c>
       <c r="G218" t="n">
-        <v>84</v>
+        <v>168</v>
       </c>
     </row>
     <row r="219">
@@ -5905,19 +5905,19 @@
         <v>46061</v>
       </c>
       <c r="C219" t="n">
-        <v>0.855072463768116</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D219" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.1488095238095238</v>
       </c>
       <c r="E219" t="n">
-        <v>0.4107142857142857</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
         <v>168</v>
       </c>
       <c r="G219" t="n">
-        <v>69</v>
+        <v>168</v>
       </c>
     </row>
     <row r="220">
@@ -5936,13 +5936,13 @@
         <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>0.3690476190476191</v>
+        <v>1</v>
       </c>
       <c r="F220" t="n">
         <v>168</v>
       </c>
       <c r="G220" t="n">
-        <v>62</v>
+        <v>168</v>
       </c>
     </row>
     <row r="221">
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>0.3154761904761905</v>
+        <v>1</v>
       </c>
       <c r="F221" t="n">
         <v>168</v>
       </c>
       <c r="G221" t="n">
-        <v>53</v>
+        <v>168</v>
       </c>
     </row>
     <row r="222">
@@ -5986,13 +5986,13 @@
         <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="F222" t="n">
         <v>168</v>
       </c>
       <c r="G222" t="n">
-        <v>56</v>
+        <v>168</v>
       </c>
     </row>
     <row r="223">
@@ -6005,19 +6005,19 @@
         <v>46089</v>
       </c>
       <c r="C223" t="n">
-        <v>0.9014084507042254</v>
+        <v>0.9404761904761905</v>
       </c>
       <c r="D223" t="n">
-        <v>0.04225352112676056</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="E223" t="n">
-        <v>0.4226190476190476</v>
+        <v>1</v>
       </c>
       <c r="F223" t="n">
         <v>168</v>
       </c>
       <c r="G223" t="n">
-        <v>71</v>
+        <v>168</v>
       </c>
     </row>
     <row r="224">
@@ -6036,13 +6036,13 @@
         <v>0</v>
       </c>
       <c r="E224" t="n">
-        <v>0.3988095238095238</v>
+        <v>1</v>
       </c>
       <c r="F224" t="n">
         <v>168</v>
       </c>
       <c r="G224" t="n">
-        <v>67</v>
+        <v>168</v>
       </c>
     </row>
     <row r="225">
@@ -6061,13 +6061,13 @@
         <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>0.2619047619047619</v>
+        <v>1</v>
       </c>
       <c r="F225" t="n">
         <v>168</v>
       </c>
       <c r="G225" t="n">
-        <v>44</v>
+        <v>168</v>
       </c>
     </row>
     <row r="226">
@@ -6086,13 +6086,13 @@
         <v>0</v>
       </c>
       <c r="E226" t="n">
-        <v>0.4166666666666667</v>
+        <v>1</v>
       </c>
       <c r="F226" t="n">
         <v>168</v>
       </c>
       <c r="G226" t="n">
-        <v>70</v>
+        <v>168</v>
       </c>
     </row>
     <row r="227">
@@ -6105,19 +6105,19 @@
         <v>46117</v>
       </c>
       <c r="C227" t="n">
-        <v>0.7840909090909091</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="D227" t="n">
-        <v>0.125</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="E227" t="n">
-        <v>0.5238095238095238</v>
+        <v>1</v>
       </c>
       <c r="F227" t="n">
         <v>168</v>
       </c>
       <c r="G227" t="n">
-        <v>88</v>
+        <v>168</v>
       </c>
     </row>
     <row r="228">
@@ -6130,19 +6130,19 @@
         <v>46124</v>
       </c>
       <c r="C228" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="D228" t="n">
-        <v>0.09183673469387756</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E228" t="n">
-        <v>0.5833333333333334</v>
+        <v>1</v>
       </c>
       <c r="F228" t="n">
         <v>168</v>
       </c>
       <c r="G228" t="n">
-        <v>98</v>
+        <v>168</v>
       </c>
     </row>
     <row r="229">
@@ -6154,16 +6154,20 @@
       <c r="B229" s="2" t="n">
         <v>46131</v>
       </c>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
+      <c r="C229" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.1</v>
+      </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F229" t="n">
         <v>24</v>
       </c>
       <c r="G229" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="230">
@@ -6201,10 +6205,10 @@
         <v>45879</v>
       </c>
       <c r="C231" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="D231" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="E231" t="n">
         <v>1</v>
@@ -6226,19 +6230,19 @@
         <v>45886</v>
       </c>
       <c r="C232" t="n">
-        <v>0.703125</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="D232" t="n">
-        <v>0.0625</v>
+        <v>0.125</v>
       </c>
       <c r="E232" t="n">
-        <v>0.3809523809523809</v>
+        <v>1</v>
       </c>
       <c r="F232" t="n">
         <v>168</v>
       </c>
       <c r="G232" t="n">
-        <v>64</v>
+        <v>168</v>
       </c>
     </row>
     <row r="233">
@@ -6251,19 +6255,19 @@
         <v>45893</v>
       </c>
       <c r="C233" t="n">
-        <v>0.9664429530201343</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="D233" t="n">
-        <v>0.03355704697986577</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="E233" t="n">
-        <v>0.8869047619047619</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
         <v>168</v>
       </c>
       <c r="G233" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="234">
@@ -6276,10 +6280,10 @@
         <v>45900</v>
       </c>
       <c r="C234" t="n">
-        <v>0.7261904761904762</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="D234" t="n">
-        <v>0.1488095238095238</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="E234" t="n">
         <v>1</v>
@@ -6301,19 +6305,19 @@
         <v>45907</v>
       </c>
       <c r="C235" t="n">
-        <v>0.6204819277108434</v>
+        <v>0.6369047619047619</v>
       </c>
       <c r="D235" t="n">
-        <v>0.2289156626506024</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="E235" t="n">
-        <v>0.9880952380952381</v>
+        <v>1</v>
       </c>
       <c r="F235" t="n">
         <v>168</v>
       </c>
       <c r="G235" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="236">
@@ -6326,19 +6330,19 @@
         <v>45914</v>
       </c>
       <c r="C236" t="n">
-        <v>0.7232142857142857</v>
+        <v>0.7517241379310344</v>
       </c>
       <c r="D236" t="n">
-        <v>0.0625</v>
+        <v>0.06896551724137931</v>
       </c>
       <c r="E236" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8630952380952381</v>
       </c>
       <c r="F236" t="n">
         <v>168</v>
       </c>
       <c r="G236" t="n">
-        <v>112</v>
+        <v>145</v>
       </c>
     </row>
     <row r="237">
@@ -6351,19 +6355,19 @@
         <v>45921</v>
       </c>
       <c r="C237" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D237" t="n">
-        <v>0.141025641025641</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="E237" t="n">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
       <c r="F237" t="n">
         <v>168</v>
       </c>
       <c r="G237" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
     </row>
     <row r="238">
@@ -6376,19 +6380,19 @@
         <v>45928</v>
       </c>
       <c r="C238" t="n">
-        <v>0.8581560283687943</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="D238" t="n">
-        <v>0.1276595744680851</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="E238" t="n">
-        <v>0.8392857142857143</v>
+        <v>1</v>
       </c>
       <c r="F238" t="n">
         <v>168</v>
       </c>
       <c r="G238" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
     </row>
     <row r="239">
@@ -6401,19 +6405,19 @@
         <v>45935</v>
       </c>
       <c r="C239" t="n">
-        <v>0.6201550387596899</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="D239" t="n">
-        <v>0.1550387596899225</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E239" t="n">
-        <v>0.7678571428571429</v>
+        <v>1</v>
       </c>
       <c r="F239" t="n">
         <v>168</v>
       </c>
       <c r="G239" t="n">
-        <v>129</v>
+        <v>168</v>
       </c>
     </row>
     <row r="240">
@@ -6426,19 +6430,19 @@
         <v>45942</v>
       </c>
       <c r="C240" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="D240" t="n">
-        <v>0.02564102564102564</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="E240" t="n">
-        <v>0.6964285714285714</v>
+        <v>1</v>
       </c>
       <c r="F240" t="n">
         <v>168</v>
       </c>
       <c r="G240" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
     </row>
     <row r="241">
@@ -6451,19 +6455,19 @@
         <v>45949</v>
       </c>
       <c r="C241" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="D241" t="n">
-        <v>0.1032258064516129</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="E241" t="n">
-        <v>0.9226190476190477</v>
+        <v>1</v>
       </c>
       <c r="F241" t="n">
         <v>168</v>
       </c>
       <c r="G241" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="242">
@@ -6476,10 +6480,10 @@
         <v>45956</v>
       </c>
       <c r="C242" t="n">
-        <v>0.4345238095238095</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="D242" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="E242" t="n">
         <v>1</v>
@@ -6501,19 +6505,19 @@
         <v>45963</v>
       </c>
       <c r="C243" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="D243" t="n">
-        <v>0.1029411764705882</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="E243" t="n">
-        <v>0.8095238095238095</v>
+        <v>1</v>
       </c>
       <c r="F243" t="n">
         <v>168</v>
       </c>
       <c r="G243" t="n">
-        <v>136</v>
+        <v>168</v>
       </c>
     </row>
     <row r="244">
@@ -6526,19 +6530,19 @@
         <v>45970</v>
       </c>
       <c r="C244" t="n">
-        <v>0.6792452830188679</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="D244" t="n">
-        <v>0.2578616352201258</v>
+        <v>0.3035714285714285</v>
       </c>
       <c r="E244" t="n">
-        <v>0.9464285714285714</v>
+        <v>1</v>
       </c>
       <c r="F244" t="n">
         <v>168</v>
       </c>
       <c r="G244" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="245">
@@ -6551,19 +6555,19 @@
         <v>45977</v>
       </c>
       <c r="C245" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.6011904761904762</v>
       </c>
       <c r="D245" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="E245" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="F245" t="n">
         <v>168</v>
       </c>
       <c r="G245" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="246">
@@ -6576,19 +6580,19 @@
         <v>45984</v>
       </c>
       <c r="C246" t="n">
-        <v>0.4855072463768116</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="D246" t="n">
-        <v>0.2318840579710145</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="E246" t="n">
-        <v>0.8214285714285714</v>
+        <v>1</v>
       </c>
       <c r="F246" t="n">
         <v>168</v>
       </c>
       <c r="G246" t="n">
-        <v>138</v>
+        <v>168</v>
       </c>
     </row>
     <row r="247">
@@ -6601,19 +6605,19 @@
         <v>45991</v>
       </c>
       <c r="C247" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="D247" t="n">
-        <v>0.1043478260869565</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="E247" t="n">
-        <v>0.6845238095238095</v>
+        <v>1</v>
       </c>
       <c r="F247" t="n">
         <v>168</v>
       </c>
       <c r="G247" t="n">
-        <v>115</v>
+        <v>168</v>
       </c>
     </row>
     <row r="248">
@@ -6632,13 +6636,13 @@
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>0.1607142857142857</v>
+        <v>1</v>
       </c>
       <c r="F248" t="n">
         <v>168</v>
       </c>
       <c r="G248" t="n">
-        <v>27</v>
+        <v>168</v>
       </c>
     </row>
     <row r="249">
@@ -6651,19 +6655,19 @@
         <v>46005</v>
       </c>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="E249" t="n">
-        <v>0.130952380952381</v>
+        <v>1</v>
       </c>
       <c r="F249" t="n">
         <v>168</v>
       </c>
       <c r="G249" t="n">
-        <v>22</v>
+        <v>168</v>
       </c>
     </row>
     <row r="250">
@@ -6676,19 +6680,19 @@
         <v>46012</v>
       </c>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>0.9940476190476191</v>
       </c>
       <c r="D250" t="n">
-        <v>0</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="E250" t="n">
-        <v>0.7261904761904762</v>
+        <v>1</v>
       </c>
       <c r="F250" t="n">
         <v>168</v>
       </c>
       <c r="G250" t="n">
-        <v>122</v>
+        <v>168</v>
       </c>
     </row>
     <row r="251">
@@ -6701,19 +6705,19 @@
         <v>46019</v>
       </c>
       <c r="C251" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9464285714285714</v>
       </c>
       <c r="D251" t="n">
-        <v>0.06521739130434782</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="E251" t="n">
-        <v>0.5476190476190477</v>
+        <v>1</v>
       </c>
       <c r="F251" t="n">
         <v>168</v>
       </c>
       <c r="G251" t="n">
-        <v>92</v>
+        <v>168</v>
       </c>
     </row>
     <row r="252">
@@ -6726,19 +6730,19 @@
         <v>46026</v>
       </c>
       <c r="C252" t="n">
-        <v>0.8481012658227848</v>
+        <v>0.6845238095238095</v>
       </c>
       <c r="D252" t="n">
-        <v>0.1265822784810127</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="E252" t="n">
-        <v>0.9404761904761905</v>
+        <v>1</v>
       </c>
       <c r="F252" t="n">
         <v>168</v>
       </c>
       <c r="G252" t="n">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="253">
@@ -6751,19 +6755,19 @@
         <v>46033</v>
       </c>
       <c r="C253" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="D253" t="n">
-        <v>0.3492063492063492</v>
+        <v>0.3115942028985507</v>
       </c>
       <c r="E253" t="n">
-        <v>0.75</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="F253" t="n">
         <v>168</v>
       </c>
       <c r="G253" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="254">
@@ -6776,19 +6780,19 @@
         <v>46040</v>
       </c>
       <c r="C254" t="n">
-        <v>0.4315068493150685</v>
+        <v>0.3869047619047619</v>
       </c>
       <c r="D254" t="n">
-        <v>0.2054794520547945</v>
+        <v>0.244047619047619</v>
       </c>
       <c r="E254" t="n">
-        <v>0.8690476190476191</v>
+        <v>1</v>
       </c>
       <c r="F254" t="n">
         <v>168</v>
       </c>
       <c r="G254" t="n">
-        <v>146</v>
+        <v>168</v>
       </c>
     </row>
     <row r="255">
@@ -6801,19 +6805,19 @@
         <v>46047</v>
       </c>
       <c r="C255" t="n">
-        <v>0.5858585858585859</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D255" t="n">
-        <v>0.2828282828282828</v>
+        <v>0.2976190476190476</v>
       </c>
       <c r="E255" t="n">
-        <v>0.5892857142857143</v>
+        <v>1</v>
       </c>
       <c r="F255" t="n">
         <v>168</v>
       </c>
       <c r="G255" t="n">
-        <v>99</v>
+        <v>168</v>
       </c>
     </row>
     <row r="256">
@@ -6826,19 +6830,19 @@
         <v>46054</v>
       </c>
       <c r="C256" t="n">
-        <v>0.6167664670658682</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="D256" t="n">
-        <v>0.1137724550898204</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="E256" t="n">
-        <v>0.9940476190476191</v>
+        <v>1</v>
       </c>
       <c r="F256" t="n">
         <v>168</v>
       </c>
       <c r="G256" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="257">
@@ -6851,19 +6855,19 @@
         <v>46061</v>
       </c>
       <c r="C257" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="D257" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E257" t="n">
-        <v>0.4404761904761905</v>
+        <v>1</v>
       </c>
       <c r="F257" t="n">
         <v>168</v>
       </c>
       <c r="G257" t="n">
-        <v>74</v>
+        <v>168</v>
       </c>
     </row>
     <row r="258">
@@ -6876,19 +6880,19 @@
         <v>46068</v>
       </c>
       <c r="C258" t="n">
-        <v>1</v>
+        <v>0.7559523809523809</v>
       </c>
       <c r="D258" t="n">
-        <v>0</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="E258" t="n">
-        <v>0.005952380952380952</v>
+        <v>1</v>
       </c>
       <c r="F258" t="n">
         <v>168</v>
       </c>
       <c r="G258" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
     </row>
     <row r="259">
@@ -6901,19 +6905,19 @@
         <v>46075</v>
       </c>
       <c r="C259" t="n">
-        <v>0.64</v>
+        <v>0.6547619047619048</v>
       </c>
       <c r="D259" t="n">
-        <v>0.04</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E259" t="n">
-        <v>0.1488095238095238</v>
+        <v>1</v>
       </c>
       <c r="F259" t="n">
         <v>168</v>
       </c>
       <c r="G259" t="n">
-        <v>25</v>
+        <v>168</v>
       </c>
     </row>
     <row r="260">
@@ -6926,19 +6930,19 @@
         <v>46082</v>
       </c>
       <c r="C260" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="D260" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="E260" t="n">
-        <v>0.1547619047619048</v>
+        <v>1</v>
       </c>
       <c r="F260" t="n">
         <v>168</v>
       </c>
       <c r="G260" t="n">
-        <v>26</v>
+        <v>168</v>
       </c>
     </row>
     <row r="261">
@@ -6951,19 +6955,19 @@
         <v>46089</v>
       </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>0.9940476190476191</v>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="E261" t="n">
-        <v>0.07142857142857142</v>
+        <v>1</v>
       </c>
       <c r="F261" t="n">
         <v>168</v>
       </c>
       <c r="G261" t="n">
-        <v>12</v>
+        <v>168</v>
       </c>
     </row>
     <row r="262">
@@ -6982,13 +6986,13 @@
         <v>0</v>
       </c>
       <c r="E262" t="n">
-        <v>0.01785714285714286</v>
+        <v>1</v>
       </c>
       <c r="F262" t="n">
         <v>168</v>
       </c>
       <c r="G262" t="n">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="263">
@@ -7007,13 +7011,13 @@
         <v>0</v>
       </c>
       <c r="E263" t="n">
-        <v>0.08928571428571429</v>
+        <v>1</v>
       </c>
       <c r="F263" t="n">
         <v>168</v>
       </c>
       <c r="G263" t="n">
-        <v>15</v>
+        <v>168</v>
       </c>
     </row>
     <row r="264">
@@ -7026,19 +7030,19 @@
         <v>46110</v>
       </c>
       <c r="C264" t="n">
-        <v>0.8354430379746836</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="D264" t="n">
-        <v>0.08860759493670886</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="E264" t="n">
-        <v>0.4702380952380952</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
         <v>168</v>
       </c>
       <c r="G264" t="n">
-        <v>79</v>
+        <v>168</v>
       </c>
     </row>
     <row r="265">
@@ -7051,19 +7055,19 @@
         <v>46117</v>
       </c>
       <c r="C265" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.6726190476190477</v>
       </c>
       <c r="D265" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="E265" t="n">
-        <v>0.7916666666666666</v>
+        <v>1</v>
       </c>
       <c r="F265" t="n">
         <v>168</v>
       </c>
       <c r="G265" t="n">
-        <v>133</v>
+        <v>168</v>
       </c>
     </row>
     <row r="266">
@@ -7076,19 +7080,19 @@
         <v>46124</v>
       </c>
       <c r="C266" t="n">
-        <v>0.3443708609271523</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="D266" t="n">
-        <v>0.1854304635761589</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E266" t="n">
-        <v>0.8988095238095238</v>
+        <v>1</v>
       </c>
       <c r="F266" t="n">
         <v>168</v>
       </c>
       <c r="G266" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="267">
@@ -7101,19 +7105,19 @@
         <v>46131</v>
       </c>
       <c r="C267" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.65</v>
       </c>
       <c r="D267" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.3</v>
       </c>
       <c r="E267" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F267" t="n">
         <v>24</v>
       </c>
       <c r="G267" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -7177,10 +7181,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2316</v>
+        <v>569</v>
       </c>
       <c r="D2" t="n">
-        <v>2316</v>
+        <v>569</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -7208,10 +7212,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="D3" t="n">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -7239,10 +7243,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="D4" t="n">
-        <v>1060</v>
+        <v>1106</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -7301,10 +7305,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -7332,10 +7336,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7363,10 +7367,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -7394,10 +7398,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>465</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>

--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_3_burden_coverage_calibration_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_3_burden_coverage_calibration_source_data.xlsx
@@ -7131,7 +7131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7167,6 +7167,16 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>exact_independent_blocks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>percentile_precision_grade</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>stratum</t>
         </is>
       </c>
@@ -7196,7 +7206,15 @@
           <t>adequate</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>wide_interval</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>DO R0</t>
         </is>
@@ -7227,7 +7245,15 @@
           <t>adequate</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>DO R1</t>
         </is>
@@ -7258,7 +7284,15 @@
           <t>adequate</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>DO R2</t>
         </is>
@@ -7289,7 +7323,15 @@
           <t>adequate</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>DO R3</t>
         </is>
@@ -7320,7 +7362,15 @@
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>ORP R0</t>
         </is>
@@ -7351,7 +7401,15 @@
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>ORP R1</t>
         </is>
@@ -7382,7 +7440,15 @@
           <t>adequate</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>ORP R2</t>
         </is>
@@ -7413,7 +7479,15 @@
           <t>limited_regime_support</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>ORP R3</t>
         </is>
